--- a/l9.xlsx
+++ b/l9.xlsx
@@ -20,6 +20,7 @@
     <sheet name="الضواغط" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="المكبس" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="المحطات" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="كهربا" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -759,6 +760,77 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
